--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28728,7 +28728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3115"/>
+  <dimension ref="A1:C3116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63000,6 +63000,17 @@
       </c>
       <c r="C3115" t="n">
         <v>206000</v>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B3116" t="n">
+        <v>196000</v>
+      </c>
+      <c r="C3116" t="n">
+        <v>196000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -3875,7 +3875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5205,10 +5205,10 @@
         <v>43374</v>
       </c>
       <c r="B157" t="n">
-        <v>11.66641</v>
+        <v>11.666416</v>
       </c>
       <c r="C157" t="n">
-        <v>11.66641</v>
+        <v>11.666416</v>
       </c>
     </row>
     <row r="158">
@@ -5216,10 +5216,10 @@
         <v>43466</v>
       </c>
       <c r="B158" t="n">
-        <v>11.49991</v>
+        <v>11.49992</v>
       </c>
       <c r="C158" t="n">
-        <v>11.49991</v>
+        <v>11.49992</v>
       </c>
     </row>
     <row r="159">
@@ -5260,10 +5260,10 @@
         <v>43831</v>
       </c>
       <c r="B162" t="n">
-        <v>11.591159</v>
+        <v>11.591164</v>
       </c>
       <c r="C162" t="n">
-        <v>11.591159</v>
+        <v>11.591164</v>
       </c>
     </row>
     <row r="163">
@@ -5326,10 +5326,10 @@
         <v>44378</v>
       </c>
       <c r="B168" t="n">
-        <v>10.009588</v>
+        <v>10.009597</v>
       </c>
       <c r="C168" t="n">
-        <v>10.009588</v>
+        <v>10.009597</v>
       </c>
     </row>
     <row r="169">
@@ -5436,10 +5436,10 @@
         <v>45292</v>
       </c>
       <c r="B178" t="n">
-        <v>11.058904</v>
+        <v>11.058908</v>
       </c>
       <c r="C178" t="n">
-        <v>11.058904</v>
+        <v>11.058908</v>
       </c>
     </row>
     <row r="179">
@@ -5458,10 +5458,10 @@
         <v>45474</v>
       </c>
       <c r="B180" t="n">
-        <v>11.138759</v>
+        <v>11.138762</v>
       </c>
       <c r="C180" t="n">
-        <v>11.138759</v>
+        <v>11.138762</v>
       </c>
     </row>
     <row r="181">
@@ -5469,10 +5469,10 @@
         <v>45566</v>
       </c>
       <c r="B181" t="n">
-        <v>11.122486</v>
+        <v>11.12249</v>
       </c>
       <c r="C181" t="n">
-        <v>11.122486</v>
+        <v>11.12249</v>
       </c>
     </row>
     <row r="182">
@@ -5480,10 +5480,10 @@
         <v>45658</v>
       </c>
       <c r="B182" t="n">
-        <v>11.105381</v>
+        <v>11.105386</v>
       </c>
       <c r="C182" t="n">
-        <v>11.105381</v>
+        <v>11.105386</v>
       </c>
     </row>
     <row r="183">
@@ -5491,10 +5491,10 @@
         <v>45748</v>
       </c>
       <c r="B183" t="n">
-        <v>11.124241</v>
+        <v>11.124247</v>
       </c>
       <c r="C183" t="n">
-        <v>11.124241</v>
+        <v>11.124247</v>
       </c>
     </row>
     <row r="184">
@@ -5502,10 +5502,10 @@
         <v>45839</v>
       </c>
       <c r="B184" t="n">
-        <v>11.229451</v>
+        <v>11.229457</v>
       </c>
       <c r="C184" t="n">
-        <v>11.229451</v>
+        <v>11.229457</v>
       </c>
     </row>
     <row r="185">
@@ -5513,10 +5513,10 @@
         <v>45931</v>
       </c>
       <c r="B185" t="n">
-        <v>11.322759</v>
+        <v>11.322763</v>
       </c>
       <c r="C185" t="n">
-        <v>11.322759</v>
+        <v>11.322763</v>
       </c>
     </row>
     <row r="186">
@@ -5524,10 +5524,21 @@
         <v>46023</v>
       </c>
       <c r="B186" t="n">
-        <v>11.164138</v>
+        <v>11.158929</v>
       </c>
       <c r="C186" t="n">
-        <v>11.164138</v>
+        <v>11.158929</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B187" t="n">
+        <v>11.111439</v>
+      </c>
+      <c r="C187" t="n">
+        <v>11.111439</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28739,7 +28739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3116"/>
+  <dimension ref="A1:C3117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63007,10 +63007,10 @@
         <v>46270</v>
       </c>
       <c r="B3115" t="n">
-        <v>206000</v>
+        <v>207000</v>
       </c>
       <c r="C3115" t="n">
-        <v>206000</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="3116">
@@ -63018,10 +63018,21 @@
         <v>46277</v>
       </c>
       <c r="B3116" t="n">
-        <v>196000</v>
+        <v>198000</v>
       </c>
       <c r="C3116" t="n">
-        <v>196000</v>
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3117" t="n">
+        <v>197000</v>
+      </c>
+      <c r="C3117" t="n">
+        <v>197000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14909,7 +14909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C309"/>
+  <dimension ref="A1:C310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18311,10 +18311,21 @@
         <v>46204</v>
       </c>
       <c r="B309" t="n">
-        <v>7271</v>
+        <v>7335</v>
       </c>
       <c r="C309" t="n">
-        <v>7.271</v>
+        <v>7.335</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B310" t="n">
+        <v>7079</v>
+      </c>
+      <c r="C310" t="n">
+        <v>7.079</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -63057,7 +63057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C812"/>
+  <dimension ref="A1:C813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71266,10 +71266,10 @@
         <v>44197</v>
       </c>
       <c r="B746" t="n">
-        <v>18194</v>
+        <v>18207.3</v>
       </c>
       <c r="C746" t="n">
-        <v>18194</v>
+        <v>18207.3</v>
       </c>
     </row>
     <row r="747">
@@ -71277,10 +71277,10 @@
         <v>44228</v>
       </c>
       <c r="B747" t="n">
-        <v>16697.3</v>
+        <v>16695.6</v>
       </c>
       <c r="C747" t="n">
-        <v>16697.3</v>
+        <v>16695.6</v>
       </c>
     </row>
     <row r="748">
@@ -71288,10 +71288,10 @@
         <v>44256</v>
       </c>
       <c r="B748" t="n">
-        <v>20520</v>
+        <v>20510.3</v>
       </c>
       <c r="C748" t="n">
-        <v>20520</v>
+        <v>20510.3</v>
       </c>
     </row>
     <row r="749">
@@ -71299,10 +71299,10 @@
         <v>44287</v>
       </c>
       <c r="B749" t="n">
-        <v>17420.7</v>
+        <v>17406.3</v>
       </c>
       <c r="C749" t="n">
-        <v>17420.7</v>
+        <v>17406.3</v>
       </c>
     </row>
     <row r="750">
@@ -71310,10 +71310,10 @@
         <v>44317</v>
       </c>
       <c r="B750" t="n">
-        <v>16922.4</v>
+        <v>16916.5</v>
       </c>
       <c r="C750" t="n">
-        <v>16922.4</v>
+        <v>16916.5</v>
       </c>
     </row>
     <row r="751">
@@ -71321,10 +71321,10 @@
         <v>44348</v>
       </c>
       <c r="B751" t="n">
-        <v>16838.1</v>
+        <v>16839.3</v>
       </c>
       <c r="C751" t="n">
-        <v>16838.1</v>
+        <v>16839.3</v>
       </c>
     </row>
     <row r="752">
@@ -71332,10 +71332,10 @@
         <v>44378</v>
       </c>
       <c r="B752" t="n">
-        <v>16949.3</v>
+        <v>16968</v>
       </c>
       <c r="C752" t="n">
-        <v>16949.3</v>
+        <v>16968</v>
       </c>
     </row>
     <row r="753">
@@ -71343,10 +71343,10 @@
         <v>44409</v>
       </c>
       <c r="B753" t="n">
-        <v>16917.1</v>
+        <v>16950.2</v>
       </c>
       <c r="C753" t="n">
-        <v>16917.1</v>
+        <v>16950.2</v>
       </c>
     </row>
     <row r="754">
@@ -71354,10 +71354,10 @@
         <v>44440</v>
       </c>
       <c r="B754" t="n">
-        <v>16728.5</v>
+        <v>16772.1</v>
       </c>
       <c r="C754" t="n">
-        <v>16728.5</v>
+        <v>16772.1</v>
       </c>
     </row>
     <row r="755">
@@ -71365,10 +71365,10 @@
         <v>44470</v>
       </c>
       <c r="B755" t="n">
-        <v>16733.5</v>
+        <v>16775.8</v>
       </c>
       <c r="C755" t="n">
-        <v>16733.5</v>
+        <v>16775.8</v>
       </c>
     </row>
     <row r="756">
@@ -71376,10 +71376,10 @@
         <v>44501</v>
       </c>
       <c r="B756" t="n">
-        <v>16686.4</v>
+        <v>16727.1</v>
       </c>
       <c r="C756" t="n">
-        <v>16686.4</v>
+        <v>16727.1</v>
       </c>
     </row>
     <row r="757">
@@ -71387,10 +71387,10 @@
         <v>44531</v>
       </c>
       <c r="B757" t="n">
-        <v>16610.8</v>
+        <v>16647.1</v>
       </c>
       <c r="C757" t="n">
-        <v>16610.8</v>
+        <v>16647.1</v>
       </c>
     </row>
     <row r="758">
@@ -71398,10 +71398,10 @@
         <v>44562</v>
       </c>
       <c r="B758" t="n">
-        <v>16206.1</v>
+        <v>16235.8</v>
       </c>
       <c r="C758" t="n">
-        <v>16206.1</v>
+        <v>16235.8</v>
       </c>
     </row>
     <row r="759">
@@ -71409,10 +71409,10 @@
         <v>44593</v>
       </c>
       <c r="B759" t="n">
-        <v>16207.6</v>
+        <v>16227.2</v>
       </c>
       <c r="C759" t="n">
-        <v>16207.6</v>
+        <v>16227.2</v>
       </c>
     </row>
     <row r="760">
@@ -71420,10 +71420,10 @@
         <v>44621</v>
       </c>
       <c r="B760" t="n">
-        <v>16127.2</v>
+        <v>16140.3</v>
       </c>
       <c r="C760" t="n">
-        <v>16127.2</v>
+        <v>16140.3</v>
       </c>
     </row>
     <row r="761">
@@ -71431,10 +71431,10 @@
         <v>44652</v>
       </c>
       <c r="B761" t="n">
-        <v>16125.5</v>
+        <v>16146.3</v>
       </c>
       <c r="C761" t="n">
-        <v>16125.5</v>
+        <v>16146.3</v>
       </c>
     </row>
     <row r="762">
@@ -71442,10 +71442,10 @@
         <v>44682</v>
       </c>
       <c r="B762" t="n">
-        <v>16103</v>
+        <v>16123.3</v>
       </c>
       <c r="C762" t="n">
-        <v>16103</v>
+        <v>16123.3</v>
       </c>
     </row>
     <row r="763">
@@ -71453,10 +71453,10 @@
         <v>44713</v>
       </c>
       <c r="B763" t="n">
-        <v>16062.9</v>
+        <v>16081.5</v>
       </c>
       <c r="C763" t="n">
-        <v>16062.9</v>
+        <v>16081.5</v>
       </c>
     </row>
     <row r="764">
@@ -71464,10 +71464,10 @@
         <v>44743</v>
       </c>
       <c r="B764" t="n">
-        <v>16270.4</v>
+        <v>16264.8</v>
       </c>
       <c r="C764" t="n">
-        <v>16270.4</v>
+        <v>16264.8</v>
       </c>
     </row>
     <row r="765">
@@ -71475,10 +71475,10 @@
         <v>44774</v>
       </c>
       <c r="B765" t="n">
-        <v>16367.3</v>
+        <v>16370.1</v>
       </c>
       <c r="C765" t="n">
-        <v>16367.3</v>
+        <v>16370.1</v>
       </c>
     </row>
     <row r="766">
@@ -71486,10 +71486,10 @@
         <v>44805</v>
       </c>
       <c r="B766" t="n">
-        <v>16423.8</v>
+        <v>16432.6</v>
       </c>
       <c r="C766" t="n">
-        <v>16423.8</v>
+        <v>16432.6</v>
       </c>
     </row>
     <row r="767">
@@ -71497,10 +71497,10 @@
         <v>44835</v>
       </c>
       <c r="B767" t="n">
-        <v>16476.3</v>
+        <v>16480.2</v>
       </c>
       <c r="C767" t="n">
-        <v>16476.3</v>
+        <v>16480.2</v>
       </c>
     </row>
     <row r="768">
@@ -71508,10 +71508,10 @@
         <v>44866</v>
       </c>
       <c r="B768" t="n">
-        <v>16502.7</v>
+        <v>16511.2</v>
       </c>
       <c r="C768" t="n">
-        <v>16502.7</v>
+        <v>16511.2</v>
       </c>
     </row>
     <row r="769">
@@ -71519,10 +71519,10 @@
         <v>44896</v>
       </c>
       <c r="B769" t="n">
-        <v>16578.2</v>
+        <v>16590.5</v>
       </c>
       <c r="C769" t="n">
-        <v>16578.2</v>
+        <v>16590.5</v>
       </c>
     </row>
     <row r="770">
@@ -71530,10 +71530,10 @@
         <v>44927</v>
       </c>
       <c r="B770" t="n">
-        <v>16906.9</v>
+        <v>16911.9</v>
       </c>
       <c r="C770" t="n">
-        <v>16906.9</v>
+        <v>16911.9</v>
       </c>
     </row>
     <row r="771">
@@ -71541,10 +71541,10 @@
         <v>44958</v>
       </c>
       <c r="B771" t="n">
-        <v>16998.2</v>
+        <v>17003.9</v>
       </c>
       <c r="C771" t="n">
-        <v>16998.2</v>
+        <v>17003.9</v>
       </c>
     </row>
     <row r="772">
@@ -71552,10 +71552,10 @@
         <v>44986</v>
       </c>
       <c r="B772" t="n">
-        <v>17098.8</v>
+        <v>17092.8</v>
       </c>
       <c r="C772" t="n">
-        <v>17098.8</v>
+        <v>17092.8</v>
       </c>
     </row>
     <row r="773">
@@ -71563,10 +71563,10 @@
         <v>45017</v>
       </c>
       <c r="B773" t="n">
-        <v>17135.3</v>
+        <v>17149.6</v>
       </c>
       <c r="C773" t="n">
-        <v>17135.3</v>
+        <v>17149.6</v>
       </c>
     </row>
     <row r="774">
@@ -71574,10 +71574,10 @@
         <v>45047</v>
       </c>
       <c r="B774" t="n">
-        <v>17196.7</v>
+        <v>17216.3</v>
       </c>
       <c r="C774" t="n">
-        <v>17196.7</v>
+        <v>17216.3</v>
       </c>
     </row>
     <row r="775">
@@ -71585,10 +71585,10 @@
         <v>45078</v>
       </c>
       <c r="B775" t="n">
-        <v>17216.3</v>
+        <v>17256.7</v>
       </c>
       <c r="C775" t="n">
-        <v>17216.3</v>
+        <v>17256.7</v>
       </c>
     </row>
     <row r="776">
@@ -71596,10 +71596,10 @@
         <v>45108</v>
       </c>
       <c r="B776" t="n">
-        <v>17250.6</v>
+        <v>17305.2</v>
       </c>
       <c r="C776" t="n">
-        <v>17250.6</v>
+        <v>17305.2</v>
       </c>
     </row>
     <row r="777">
@@ -71607,10 +71607,10 @@
         <v>45139</v>
       </c>
       <c r="B777" t="n">
-        <v>17275.3</v>
+        <v>17348.5</v>
       </c>
       <c r="C777" t="n">
-        <v>17275.3</v>
+        <v>17348.5</v>
       </c>
     </row>
     <row r="778">
@@ -71618,10 +71618,10 @@
         <v>45170</v>
       </c>
       <c r="B778" t="n">
-        <v>17282.2</v>
+        <v>17369.5</v>
       </c>
       <c r="C778" t="n">
-        <v>17282.2</v>
+        <v>17369.5</v>
       </c>
     </row>
     <row r="779">
@@ -71629,10 +71629,10 @@
         <v>45200</v>
       </c>
       <c r="B779" t="n">
-        <v>17341.3</v>
+        <v>17435.9</v>
       </c>
       <c r="C779" t="n">
-        <v>17341.3</v>
+        <v>17435.9</v>
       </c>
     </row>
     <row r="780">
@@ -71640,10 +71640,10 @@
         <v>45231</v>
       </c>
       <c r="B780" t="n">
-        <v>17427.1</v>
+        <v>17524.8</v>
       </c>
       <c r="C780" t="n">
-        <v>17427.1</v>
+        <v>17524.8</v>
       </c>
     </row>
     <row r="781">
@@ -71651,10 +71651,10 @@
         <v>45261</v>
       </c>
       <c r="B781" t="n">
-        <v>17481.7</v>
+        <v>17589.4</v>
       </c>
       <c r="C781" t="n">
-        <v>17481.7</v>
+        <v>17589.4</v>
       </c>
     </row>
     <row r="782">
@@ -71662,10 +71662,10 @@
         <v>45292</v>
       </c>
       <c r="B782" t="n">
-        <v>17575.4</v>
+        <v>17679.6</v>
       </c>
       <c r="C782" t="n">
-        <v>17575.4</v>
+        <v>17679.6</v>
       </c>
     </row>
     <row r="783">
@@ -71673,10 +71673,10 @@
         <v>45323</v>
       </c>
       <c r="B783" t="n">
-        <v>17596.2</v>
+        <v>17681</v>
       </c>
       <c r="C783" t="n">
-        <v>17596.2</v>
+        <v>17681</v>
       </c>
     </row>
     <row r="784">
@@ -71684,10 +71684,10 @@
         <v>45352</v>
       </c>
       <c r="B784" t="n">
-        <v>17617</v>
+        <v>17699.2</v>
       </c>
       <c r="C784" t="n">
-        <v>17617</v>
+        <v>17699.2</v>
       </c>
     </row>
     <row r="785">
@@ -71695,10 +71695,10 @@
         <v>45383</v>
       </c>
       <c r="B785" t="n">
-        <v>17638.6</v>
+        <v>17747.2</v>
       </c>
       <c r="C785" t="n">
-        <v>17638.6</v>
+        <v>17747.2</v>
       </c>
     </row>
     <row r="786">
@@ -71706,10 +71706,10 @@
         <v>45413</v>
       </c>
       <c r="B786" t="n">
-        <v>17713.3</v>
+        <v>17820.5</v>
       </c>
       <c r="C786" t="n">
-        <v>17713.3</v>
+        <v>17820.5</v>
       </c>
     </row>
     <row r="787">
@@ -71717,10 +71717,10 @@
         <v>45444</v>
       </c>
       <c r="B787" t="n">
-        <v>17751.1</v>
+        <v>17869.8</v>
       </c>
       <c r="C787" t="n">
-        <v>17751.1</v>
+        <v>17869.8</v>
       </c>
     </row>
     <row r="788">
@@ -71728,10 +71728,10 @@
         <v>45474</v>
       </c>
       <c r="B788" t="n">
-        <v>17743.2</v>
+        <v>17862.8</v>
       </c>
       <c r="C788" t="n">
-        <v>17743.2</v>
+        <v>17862.8</v>
       </c>
     </row>
     <row r="789">
@@ -71739,10 +71739,10 @@
         <v>45505</v>
       </c>
       <c r="B789" t="n">
-        <v>17752.9</v>
+        <v>17865.2</v>
       </c>
       <c r="C789" t="n">
-        <v>17752.9</v>
+        <v>17865.2</v>
       </c>
     </row>
     <row r="790">
@@ -71750,10 +71750,10 @@
         <v>45536</v>
       </c>
       <c r="B790" t="n">
-        <v>17769.9</v>
+        <v>17875.4</v>
       </c>
       <c r="C790" t="n">
-        <v>17769.9</v>
+        <v>17875.4</v>
       </c>
     </row>
     <row r="791">
@@ -71761,10 +71761,10 @@
         <v>45566</v>
       </c>
       <c r="B791" t="n">
-        <v>17810.5</v>
+        <v>17914.4</v>
       </c>
       <c r="C791" t="n">
-        <v>17810.5</v>
+        <v>17914.4</v>
       </c>
     </row>
     <row r="792">
@@ -71772,10 +71772,10 @@
         <v>45597</v>
       </c>
       <c r="B792" t="n">
-        <v>17851.4</v>
+        <v>17955.4</v>
       </c>
       <c r="C792" t="n">
-        <v>17851.4</v>
+        <v>17955.4</v>
       </c>
     </row>
     <row r="793">
@@ -71783,10 +71783,10 @@
         <v>45627</v>
       </c>
       <c r="B793" t="n">
-        <v>17867.9</v>
+        <v>17963.9</v>
       </c>
       <c r="C793" t="n">
-        <v>17867.9</v>
+        <v>17963.9</v>
       </c>
     </row>
     <row r="794">
@@ -71794,10 +71794,10 @@
         <v>45658</v>
       </c>
       <c r="B794" t="n">
-        <v>17889.8</v>
+        <v>17955.6</v>
       </c>
       <c r="C794" t="n">
-        <v>17889.8</v>
+        <v>17955.6</v>
       </c>
     </row>
     <row r="795">
@@ -71805,10 +71805,10 @@
         <v>45689</v>
       </c>
       <c r="B795" t="n">
-        <v>17910.5</v>
+        <v>17957.4</v>
       </c>
       <c r="C795" t="n">
-        <v>17910.5</v>
+        <v>17957.4</v>
       </c>
     </row>
     <row r="796">
@@ -71816,10 +71816,10 @@
         <v>45717</v>
       </c>
       <c r="B796" t="n">
-        <v>18029.1</v>
+        <v>18073</v>
       </c>
       <c r="C796" t="n">
-        <v>18029.1</v>
+        <v>18073</v>
       </c>
     </row>
     <row r="797">
@@ -71827,10 +71827,10 @@
         <v>45748</v>
       </c>
       <c r="B797" t="n">
-        <v>18132.9</v>
+        <v>18190.1</v>
       </c>
       <c r="C797" t="n">
-        <v>18132.9</v>
+        <v>18190.1</v>
       </c>
     </row>
     <row r="798">
@@ -71838,10 +71838,10 @@
         <v>45778</v>
       </c>
       <c r="B798" t="n">
-        <v>17980.9</v>
+        <v>18072</v>
       </c>
       <c r="C798" t="n">
-        <v>17980.9</v>
+        <v>18072</v>
       </c>
     </row>
     <row r="799">
@@ -71849,10 +71849,10 @@
         <v>45809</v>
       </c>
       <c r="B799" t="n">
-        <v>17962.1</v>
+        <v>18088.6</v>
       </c>
       <c r="C799" t="n">
-        <v>17962.1</v>
+        <v>18088.6</v>
       </c>
     </row>
     <row r="800">
@@ -71860,10 +71860,10 @@
         <v>45839</v>
       </c>
       <c r="B800" t="n">
-        <v>18040.9</v>
+        <v>18144.4</v>
       </c>
       <c r="C800" t="n">
-        <v>18040.9</v>
+        <v>18144.4</v>
       </c>
     </row>
     <row r="801">
@@ -71871,10 +71871,10 @@
         <v>45870</v>
       </c>
       <c r="B801" t="n">
-        <v>18076.9</v>
+        <v>18174</v>
       </c>
       <c r="C801" t="n">
-        <v>18076.9</v>
+        <v>18174</v>
       </c>
     </row>
     <row r="802">
@@ -71882,10 +71882,10 @@
         <v>45901</v>
       </c>
       <c r="B802" t="n">
-        <v>18094.6</v>
+        <v>18192.7</v>
       </c>
       <c r="C802" t="n">
-        <v>18094.6</v>
+        <v>18192.7</v>
       </c>
     </row>
     <row r="803">
@@ -71893,10 +71893,10 @@
         <v>45931</v>
       </c>
       <c r="B803" t="n">
-        <v>18037.3</v>
+        <v>18168.4</v>
       </c>
       <c r="C803" t="n">
-        <v>18037.3</v>
+        <v>18168.4</v>
       </c>
     </row>
     <row r="804">
@@ -71904,10 +71904,10 @@
         <v>45962</v>
       </c>
       <c r="B804" t="n">
-        <v>18035.1</v>
+        <v>18201.5</v>
       </c>
       <c r="C804" t="n">
-        <v>18035.1</v>
+        <v>18201.5</v>
       </c>
     </row>
     <row r="805">
@@ -71915,10 +71915,10 @@
         <v>45992</v>
       </c>
       <c r="B805" t="n">
-        <v>18018.5</v>
+        <v>18208.6</v>
       </c>
       <c r="C805" t="n">
-        <v>18018.5</v>
+        <v>18208.6</v>
       </c>
     </row>
     <row r="806">
@@ -71926,10 +71926,10 @@
         <v>46023</v>
       </c>
       <c r="B806" t="n">
-        <v>18134.6</v>
+        <v>18322.5</v>
       </c>
       <c r="C806" t="n">
-        <v>18134.6</v>
+        <v>18322.5</v>
       </c>
     </row>
     <row r="807">
@@ -71937,10 +71937,10 @@
         <v>46054</v>
       </c>
       <c r="B807" t="n">
-        <v>18051.9</v>
+        <v>18284.8</v>
       </c>
       <c r="C807" t="n">
-        <v>18051.9</v>
+        <v>18284.8</v>
       </c>
     </row>
     <row r="808">
@@ -71948,10 +71948,10 @@
         <v>46082</v>
       </c>
       <c r="B808" t="n">
-        <v>18030.5</v>
+        <v>18301.6</v>
       </c>
       <c r="C808" t="n">
-        <v>18030.5</v>
+        <v>18301.6</v>
       </c>
     </row>
     <row r="809">
@@ -71959,10 +71959,10 @@
         <v>46113</v>
       </c>
       <c r="B809" t="n">
-        <v>17957.1</v>
+        <v>18231.9</v>
       </c>
       <c r="C809" t="n">
-        <v>17957.1</v>
+        <v>18231.9</v>
       </c>
     </row>
     <row r="810">
@@ -71970,10 +71970,10 @@
         <v>46143</v>
       </c>
       <c r="B810" t="n">
-        <v>18000.1</v>
+        <v>18292.8</v>
       </c>
       <c r="C810" t="n">
-        <v>18000.1</v>
+        <v>18292.8</v>
       </c>
     </row>
     <row r="811">
@@ -71981,10 +71981,10 @@
         <v>46174</v>
       </c>
       <c r="B811" t="n">
-        <v>18054.9</v>
+        <v>18358.4</v>
       </c>
       <c r="C811" t="n">
-        <v>18054.9</v>
+        <v>18358.4</v>
       </c>
     </row>
     <row r="812">
@@ -71992,10 +71992,21 @@
         <v>46204</v>
       </c>
       <c r="B812" t="n">
-        <v>18122.5</v>
+        <v>18415.4</v>
       </c>
       <c r="C812" t="n">
-        <v>18122.5</v>
+        <v>18415.4</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B813" t="n">
+        <v>18410.5</v>
+      </c>
+      <c r="C813" t="n">
+        <v>18410.5</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28750,7 +28750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3117"/>
+  <dimension ref="A1:C3118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63040,9 +63040,20 @@
         <v>46284</v>
       </c>
       <c r="B3117" t="n">
+        <v>198000</v>
+      </c>
+      <c r="C3117" t="n">
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3118" t="n">
         <v>197000</v>
       </c>
-      <c r="C3117" t="n">
+      <c r="C3118" t="n">
         <v>197000</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -18339,7 +18339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28737,6 +28737,17 @@
       </c>
       <c r="C945" t="n">
         <v>4.1</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B946" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C946" t="n">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7145,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C704"/>
+  <dimension ref="A1:C705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14826,10 +14826,10 @@
         <v>46023</v>
       </c>
       <c r="B698" t="n">
-        <v>1326040.45</v>
+        <v>1326040.46</v>
       </c>
       <c r="C698" t="n">
-        <v>1326040.45</v>
+        <v>1326040.46</v>
       </c>
     </row>
     <row r="699">
@@ -14892,10 +14892,21 @@
         <v>46204</v>
       </c>
       <c r="B704" t="n">
-        <v>1357221.44</v>
+        <v>1357200.7</v>
       </c>
       <c r="C704" t="n">
-        <v>1357221.44</v>
+        <v>1357200.7</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B705" t="n">
+        <v>1352414</v>
+      </c>
+      <c r="C705" t="n">
+        <v>1352414</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28772,7 +28772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3118"/>
+  <dimension ref="A1:C3119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63073,9 +63073,20 @@
         <v>46291</v>
       </c>
       <c r="B3118" t="n">
+        <v>199000</v>
+      </c>
+      <c r="C3118" t="n">
+        <v>199000</v>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B3119" t="n">
         <v>197000</v>
       </c>
-      <c r="C3118" t="n">
+      <c r="C3119" t="n">
         <v>197000</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28772,7 +28772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3119"/>
+  <dimension ref="A1:C3120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63084,10 +63084,21 @@
         <v>46298</v>
       </c>
       <c r="B3119" t="n">
-        <v>197000</v>
+        <v>198000</v>
       </c>
       <c r="C3119" t="n">
-        <v>197000</v>
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B3120" t="n">
+        <v>199000</v>
+      </c>
+      <c r="C3120" t="n">
+        <v>199000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28772,7 +28772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3120"/>
+  <dimension ref="A1:C3121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63095,10 +63095,21 @@
         <v>46305</v>
       </c>
       <c r="B3120" t="n">
-        <v>199000</v>
+        <v>200000</v>
       </c>
       <c r="C3120" t="n">
-        <v>199000</v>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B3121" t="n">
+        <v>194000</v>
+      </c>
+      <c r="C3121" t="n">
+        <v>194000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28772,7 +28772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3121"/>
+  <dimension ref="A1:C3122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63106,9 +63106,20 @@
         <v>46312</v>
       </c>
       <c r="B3121" t="n">
+        <v>195000</v>
+      </c>
+      <c r="C3121" t="n">
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B3122" t="n">
         <v>194000</v>
       </c>
-      <c r="C3121" t="n">
+      <c r="C3122" t="n">
         <v>194000</v>
       </c>
     </row>
@@ -63123,7 +63134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C813"/>
+  <dimension ref="A1:C814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72058,10 +72069,10 @@
         <v>46204</v>
       </c>
       <c r="B812" t="n">
-        <v>18415.4</v>
+        <v>18414.1</v>
       </c>
       <c r="C812" t="n">
-        <v>18415.4</v>
+        <v>18414.1</v>
       </c>
     </row>
     <row r="813">
@@ -72069,10 +72080,21 @@
         <v>46235</v>
       </c>
       <c r="B813" t="n">
-        <v>18410.5</v>
+        <v>18416.2</v>
       </c>
       <c r="C813" t="n">
-        <v>18410.5</v>
+        <v>18416.2</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B814" t="n">
+        <v>18366.1</v>
+      </c>
+      <c r="C814" t="n">
+        <v>18366.1</v>
       </c>
     </row>
   </sheetData>
